--- a/AAII_Financials/Quarterly/MBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>MBC</t>
   </si>
@@ -656,325 +656,338 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45193</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45102</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45011</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44920</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44829</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44556</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44374</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>815200</v>
+      </c>
+      <c r="E8" s="3">
         <v>618000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>644600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>698900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>730900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>660300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>667700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>718100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>676500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>638100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>677100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>677300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>695100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>676700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>784400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>858400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1632700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>744800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>716500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1394000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>610900</v>
+      </c>
+      <c r="E9" s="3">
         <v>461400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>477900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>480700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>491200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>458100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>464400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>480100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>445500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>433400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>466600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>441800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>461100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>472100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>569400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>593500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1172100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>556900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>516800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>997700</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>204300</v>
+      </c>
+      <c r="E10" s="3">
         <v>156600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>166700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>218200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>239700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>202200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>203300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>238000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>231000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>204700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>210500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>235500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>234000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>204600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>215000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>264900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>460600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>187900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>199700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>396300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,8 +1013,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,84 +1159,90 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E14" s="3">
         <v>12800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-6500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>34600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>27300</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1200</v>
       </c>
       <c r="U14" s="3">
         <v>1200</v>
       </c>
       <c r="V14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W14" s="3">
         <v>1800</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6400</v>
+        <v>7400</v>
       </c>
       <c r="E15" s="3">
         <v>6400</v>
@@ -1234,13 +1257,13 @@
         <v>6400</v>
       </c>
       <c r="I15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J15" s="3">
         <v>6500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3700</v>
       </c>
       <c r="L15" s="3">
         <v>3700</v>
@@ -1249,10 +1272,10 @@
         <v>3700</v>
       </c>
       <c r="N15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O15" s="3">
         <v>3600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>4000</v>
       </c>
       <c r="P15" s="3">
         <v>4000</v>
@@ -1261,31 +1284,34 @@
         <v>4000</v>
       </c>
       <c r="R15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S15" s="3">
         <v>4300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8900</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>796600</v>
+      </c>
+      <c r="E17" s="3">
         <v>623700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>660300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>639500</v>
       </c>
-      <c r="G17" s="3">
-        <v>655300</v>
-      </c>
       <c r="H17" s="3">
+        <v>655100</v>
+      </c>
+      <c r="I17" s="3">
         <v>618500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>620200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>638100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>591900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>575300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>625700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>585700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>606700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>609700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>769300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>783600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1519300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>699300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>654900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1266800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>59400</v>
       </c>
-      <c r="G18" s="3">
-        <v>75600</v>
-      </c>
       <c r="H18" s="3">
+        <v>75800</v>
+      </c>
+      <c r="I18" s="3">
         <v>41800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>47500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>80000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>84600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>62800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>51400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>91600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>88400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>67000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>74800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>113400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>45500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>61600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>127200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,198 +1510,205 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>82800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>47800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>88500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>91600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>67200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>96200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>91800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>70500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>96100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>146200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>61000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>78100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>161400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E22" s="3">
         <v>18400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>15300</v>
       </c>
       <c r="N22" s="3">
         <v>15300</v>
       </c>
       <c r="O22" s="3">
+        <v>15300</v>
+      </c>
+      <c r="P22" s="3">
         <v>17200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1681,8 +1721,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1690,150 +1730,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-36100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-43400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>49000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>19800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>49000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>77900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>69700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>47900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>78200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>115800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>46300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>63000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>129000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-20700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>26100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>27900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>29000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-42000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>45300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>59700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>51200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>52100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>87900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>47400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>100000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-42000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>45300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>59700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>51200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>52100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>87900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>47400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,150 +2396,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-42000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>45300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>59700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>51200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>52100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>87900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>47400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-42000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>45300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>59700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>51200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>52100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>87900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>47400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45193</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45102</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45011</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44920</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44829</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44556</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44374</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2829,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E41" s="3">
         <v>138400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>183300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>120100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>113500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>120600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>108400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>189400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>153700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>148700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>122500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>110200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>116300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>101100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>134000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>125800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2885,62 +2975,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E43" s="3">
         <v>217700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>150400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>218400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>218800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>221100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>191000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>216100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>213500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>224400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>203000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>233600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>235700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>278300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>289600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>326000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>332400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,62 +3049,65 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>435600</v>
+      </c>
+      <c r="E44" s="3">
         <v>271700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>269100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>272400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>277000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>288700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>276400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>299400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>270000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>247900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>249800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>269400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>319600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>349600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>373100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>416200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>375300</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,62 +3123,65 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E45" s="3">
         <v>107100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>93100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>84400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>73800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>65800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>62700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>63000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>76500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>75700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>62700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>66400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>66200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>64500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>63300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3197,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1061700</v>
+      </c>
+      <c r="E46" s="3">
         <v>734900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>695900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>690000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>689700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>689100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>650700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>686900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>745300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>702500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>677200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>684000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>728200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>810600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>830000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>940700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>896800</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3213,18 +3318,18 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>624200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>562700</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,62 +3345,65 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1115200</v>
+      </c>
+      <c r="E48" s="3">
         <v>676700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>692200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>594400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>546100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>539200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>547900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>528000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>400200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>413200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>416700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>403100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>401600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>406800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>404900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>396400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>395000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,62 +3419,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2207100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1667900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1675200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1680200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1688100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1691400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1697100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1707300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1250800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1255200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1260600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1263100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1268100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1269100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1274000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1298600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1306400</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,62 +3641,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E52" s="3">
         <v>31400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>33400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>20500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>34300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3789,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4479600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3116700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3100400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3001900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2957400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2955800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2929800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2960200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2427100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2400100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2381700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2378300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2424000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2508100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2529400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3278100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3195200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,62 +3921,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>249500</v>
+      </c>
+      <c r="E57" s="3">
         <v>175100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>203700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>182500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>176700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>182400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>180700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>175300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>173600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>163600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>151400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>179700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>182200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>202800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>219200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>209900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>236700</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,56 +3993,59 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>24300</v>
+        <v>75100</v>
       </c>
       <c r="E58" s="3">
         <v>24300</v>
       </c>
       <c r="F58" s="3">
+        <v>24300</v>
+      </c>
+      <c r="G58" s="3">
         <v>19700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>23600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>36600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>17500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3924,8 +4058,8 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -3933,62 +4067,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E59" s="3">
         <v>28500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>35300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>32900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>35400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>174400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>185500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>165400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4141,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>603700</v>
+      </c>
+      <c r="E60" s="3">
         <v>353900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>415700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>369900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>368600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>362500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>395400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>378400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>332200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>340400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>349400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>367900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>374400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>388800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>411100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>395400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>402100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,56 +4215,59 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1614700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1256000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1149700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1056500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1055600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1110400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1062800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1119000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>732700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>726900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>736500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>747700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>836200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>968000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>961500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4146,62 +4289,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E62" s="3">
         <v>16100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>8300</v>
       </c>
       <c r="P62" s="3">
         <v>8300</v>
       </c>
       <c r="Q62" s="3">
+        <v>8300</v>
+      </c>
+      <c r="R62" s="3">
         <v>147600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>178000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>179700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4585,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2510900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1796200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1755800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1618400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1596400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1649100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1635100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1672600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1168000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1171100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1187900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1221800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1316400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1461700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1520200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>573400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>581800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +4983,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1284100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1341700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1357100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1399100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1381000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1343700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1330400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1316400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1287300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1242000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1204500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1168400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1108700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1057500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1022500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2325500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2273400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5279,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1968700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1320500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1344600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1383500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1361000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1306700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1294700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1287600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1259100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1229000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1193800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1156500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1107600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1046400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1009200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2704700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2613400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45193</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45102</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45011</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44920</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44829</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44556</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44374</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-42000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>45300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>59700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>51200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>52100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>87900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>47400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,79 +5610,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E83" s="3">
         <v>16400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>30400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32400</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-133000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>55400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>84800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-31400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>115100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>80800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>77400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>69100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>142500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>131900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>62100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>117700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>41800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>76100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>62300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>76000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,70 +6156,71 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-35900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-23700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-23800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-530000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18500</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6291,8 +6525,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,217 +6774,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E100" s="3">
         <v>101600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-45800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-67500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>33500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-61700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>371600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-33200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-120100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-129300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-128000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-69600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-40600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-64000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
       </c>
       <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5800</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>68500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-80000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-32900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5900</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
